--- a/activity/M01A03/M01A03_RadioCurvatura.xlsx
+++ b/activity/M01A03/M01A03_RadioCurvatura.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC43F0A-1D32-4B18-974A-D69B362543D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3706F3-12CA-4F6E-BBB7-82AFAD86205B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="12" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="38">
   <si>
     <t>Observaciones</t>
   </si>
@@ -116,9 +116,6 @@
   </si>
   <si>
     <t>Grupo 5</t>
-  </si>
-  <si>
-    <t>https://github.com/rcfdtools/R.HCMC/blob/main/activity/M01A03/Readme.md</t>
   </si>
   <si>
     <t>M01A03</t>
@@ -232,12 +229,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <color theme="10"/>
-      <name val="Segoe UI Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -250,6 +241,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <color rgb="FF0070C0"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
@@ -269,7 +266,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -493,15 +490,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -511,7 +499,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -583,36 +571,30 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -621,10 +603,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -636,14 +621,14 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2070,25 +2055,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="F1" s="26" t="s">
-        <v>27</v>
+      <c r="F1" s="24" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
     </row>
     <row r="4" spans="2:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="20" t="s">
@@ -2111,14 +2096,14 @@
       <c r="B5" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="25">
         <v>5</v>
       </c>
       <c r="D5" s="21">
         <f>Detalle!C19*C5/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="25">
         <v>5</v>
       </c>
       <c r="F5" s="13">
@@ -2130,14 +2115,14 @@
       <c r="B6" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="25">
         <v>5</v>
       </c>
       <c r="D6" s="21">
         <f>Detalle!F19*C6/5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="27"/>
+      <c r="E6" s="25"/>
       <c r="F6" s="13">
         <f t="shared" ref="F6:F17" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
@@ -2147,14 +2132,14 @@
       <c r="B7" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="25">
         <v>5</v>
       </c>
       <c r="D7" s="21">
         <f>Detalle!I19*C7/5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="27"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2164,14 +2149,14 @@
       <c r="B8" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="25">
         <v>5</v>
       </c>
       <c r="D8" s="21">
         <f>Detalle!L19*C8/5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="27"/>
+      <c r="E8" s="25"/>
       <c r="F8" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2181,14 +2166,14 @@
       <c r="B9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="25">
         <v>5</v>
       </c>
       <c r="D9" s="21">
         <f>Detalle!O19*C9/5</f>
         <v>0</v>
       </c>
-      <c r="E9" s="27"/>
+      <c r="E9" s="25"/>
       <c r="F9" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2196,16 +2181,16 @@
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B10" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="27">
+        <v>27</v>
+      </c>
+      <c r="C10" s="25">
         <v>5</v>
       </c>
       <c r="D10" s="21">
         <f>Detalle!R19*C10/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="27"/>
+      <c r="E10" s="25"/>
       <c r="F10" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2213,16 +2198,16 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B11" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="27">
+        <v>28</v>
+      </c>
+      <c r="C11" s="25">
         <v>5</v>
       </c>
       <c r="D11" s="21">
         <f>Detalle!U19*C11/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="27"/>
+      <c r="E11" s="25"/>
       <c r="F11" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2230,16 +2215,16 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B12" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="27">
+        <v>29</v>
+      </c>
+      <c r="C12" s="25">
         <v>5</v>
       </c>
       <c r="D12" s="21">
         <f>Detalle!X19*C12/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="27"/>
+      <c r="E12" s="25"/>
       <c r="F12" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2247,16 +2232,16 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B13" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="27">
+        <v>30</v>
+      </c>
+      <c r="C13" s="25">
         <v>5</v>
       </c>
       <c r="D13" s="21">
         <f>Detalle!AA19*C13/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="27"/>
+      <c r="E13" s="25"/>
       <c r="F13" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2264,16 +2249,16 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B14" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="27">
+        <v>31</v>
+      </c>
+      <c r="C14" s="25">
         <v>5</v>
       </c>
       <c r="D14" s="21">
         <f>Detalle!AD19*C14/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="29"/>
+      <c r="E14" s="27"/>
       <c r="F14" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2281,16 +2266,16 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="27">
+        <v>32</v>
+      </c>
+      <c r="C15" s="25">
         <v>5</v>
       </c>
       <c r="D15" s="21">
         <f>Detalle!AG19*C15/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="29"/>
+      <c r="E15" s="27"/>
       <c r="F15" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2298,16 +2283,16 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B16" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="27">
+        <v>33</v>
+      </c>
+      <c r="C16" s="25">
         <v>5</v>
       </c>
       <c r="D16" s="21">
         <f>Detalle!AJ19*C16/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="29"/>
+      <c r="E16" s="27"/>
       <c r="F16" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2315,36 +2300,37 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B17" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="28">
+        <v>34</v>
+      </c>
+      <c r="C17" s="26">
         <v>5</v>
       </c>
       <c r="D17" s="22">
         <f>Detalle!AM19*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="30"/>
+      <c r="E17" s="28"/>
       <c r="F17" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
+      <c r="B18" s="42" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
+        <v>Ir a actividad M01A03 en GitHub.</v>
+      </c>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B20" s="23"/>
@@ -2354,16 +2340,15 @@
       <c r="F20" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="B2:F3"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:F19"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="B18" r:id="rId1" xr:uid="{ECF89616-0CD4-4782-AB7D-5EC340FCE9EB}"/>
-  </hyperlinks>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2428,90 +2413,90 @@
     </row>
     <row r="2" spans="1:41" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="8"/>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="41" t="str">
+      <c r="C2" s="34" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="41" t="str">
+      <c r="D2" s="35"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="34" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="42"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="41" t="str">
+      <c r="G2" s="35"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="34" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="42"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="41" t="str">
+      <c r="J2" s="35"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="34" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="42"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="41" t="str">
+      <c r="M2" s="35"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="34" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="41" t="str">
+      <c r="P2" s="35"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="34" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="S2" s="42"/>
-      <c r="T2" s="43"/>
-      <c r="U2" s="41" t="str">
+      <c r="S2" s="35"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="34" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="V2" s="42"/>
-      <c r="W2" s="43"/>
-      <c r="X2" s="41" t="str">
+      <c r="V2" s="35"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="34" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="Y2" s="42"/>
-      <c r="Z2" s="43"/>
-      <c r="AA2" s="41" t="str">
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="36"/>
+      <c r="AA2" s="34" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AB2" s="42"/>
-      <c r="AC2" s="43"/>
-      <c r="AD2" s="41" t="str">
+      <c r="AB2" s="35"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="34" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AE2" s="42"/>
-      <c r="AF2" s="43"/>
-      <c r="AG2" s="41" t="str">
+      <c r="AE2" s="35"/>
+      <c r="AF2" s="36"/>
+      <c r="AG2" s="34" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AH2" s="42"/>
-      <c r="AI2" s="43"/>
-      <c r="AJ2" s="41" t="str">
+      <c r="AH2" s="35"/>
+      <c r="AI2" s="36"/>
+      <c r="AJ2" s="34" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AK2" s="42"/>
-      <c r="AL2" s="43"/>
-      <c r="AM2" s="41" t="str">
+      <c r="AK2" s="35"/>
+      <c r="AL2" s="36"/>
+      <c r="AM2" s="34" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AN2" s="42"/>
-      <c r="AO2" s="43"/>
+      <c r="AN2" s="35"/>
+      <c r="AO2" s="36"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.45">
-      <c r="B3" s="37"/>
+      <c r="B3" s="41"/>
       <c r="C3" s="9" t="s">
         <v>1</v>
       </c>
@@ -2634,769 +2619,769 @@
       <c r="B4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="31">
-        <v>0</v>
-      </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="31">
-        <v>0</v>
-      </c>
-      <c r="G4" s="32"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="31">
-        <v>0</v>
-      </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="31">
-        <v>0</v>
-      </c>
-      <c r="M4" s="32"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="31">
-        <v>0</v>
-      </c>
-      <c r="P4" s="32"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="31">
-        <v>0</v>
-      </c>
-      <c r="S4" s="32"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="31">
-        <v>0</v>
-      </c>
-      <c r="V4" s="32"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="31">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="32"/>
-      <c r="Z4" s="33"/>
-      <c r="AA4" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="32"/>
-      <c r="AC4" s="33"/>
-      <c r="AD4" s="31">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="32"/>
-      <c r="AF4" s="33"/>
-      <c r="AG4" s="31">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="32"/>
-      <c r="AI4" s="33"/>
-      <c r="AJ4" s="31">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="32"/>
-      <c r="AL4" s="33"/>
-      <c r="AM4" s="31">
-        <v>0</v>
-      </c>
-      <c r="AN4" s="32"/>
-      <c r="AO4" s="33"/>
+      <c r="C4" s="29">
+        <v>0</v>
+      </c>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="29">
+        <v>0</v>
+      </c>
+      <c r="G4" s="30"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="29">
+        <v>0</v>
+      </c>
+      <c r="J4" s="30"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="29">
+        <v>0</v>
+      </c>
+      <c r="M4" s="30"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="29">
+        <v>0</v>
+      </c>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="29">
+        <v>0</v>
+      </c>
+      <c r="S4" s="30"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="29">
+        <v>0</v>
+      </c>
+      <c r="V4" s="30"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="30"/>
+      <c r="Z4" s="31"/>
+      <c r="AA4" s="29">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="30"/>
+      <c r="AC4" s="31"/>
+      <c r="AD4" s="29">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="30"/>
+      <c r="AF4" s="31"/>
+      <c r="AG4" s="29">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="30"/>
+      <c r="AI4" s="31"/>
+      <c r="AJ4" s="29">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="30"/>
+      <c r="AL4" s="31"/>
+      <c r="AM4" s="29">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="30"/>
+      <c r="AO4" s="31"/>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.45">
       <c r="B5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="31"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="31"/>
-      <c r="P5" s="32"/>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="31"/>
-      <c r="S5" s="32"/>
-      <c r="T5" s="33"/>
-      <c r="U5" s="31"/>
-      <c r="V5" s="32"/>
-      <c r="W5" s="33"/>
-      <c r="X5" s="31"/>
-      <c r="Y5" s="32"/>
-      <c r="Z5" s="33"/>
-      <c r="AA5" s="31"/>
-      <c r="AB5" s="32"/>
-      <c r="AC5" s="33"/>
-      <c r="AD5" s="31"/>
-      <c r="AE5" s="32"/>
-      <c r="AF5" s="33"/>
-      <c r="AG5" s="31"/>
-      <c r="AH5" s="32"/>
-      <c r="AI5" s="33"/>
-      <c r="AJ5" s="31"/>
-      <c r="AK5" s="32"/>
-      <c r="AL5" s="33"/>
-      <c r="AM5" s="31"/>
-      <c r="AN5" s="32"/>
-      <c r="AO5" s="33"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="31"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="30"/>
+      <c r="T5" s="31"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="30"/>
+      <c r="W5" s="31"/>
+      <c r="X5" s="29"/>
+      <c r="Y5" s="30"/>
+      <c r="Z5" s="31"/>
+      <c r="AA5" s="29"/>
+      <c r="AB5" s="30"/>
+      <c r="AC5" s="31"/>
+      <c r="AD5" s="29"/>
+      <c r="AE5" s="30"/>
+      <c r="AF5" s="31"/>
+      <c r="AG5" s="29"/>
+      <c r="AH5" s="30"/>
+      <c r="AI5" s="31"/>
+      <c r="AJ5" s="29"/>
+      <c r="AK5" s="30"/>
+      <c r="AL5" s="31"/>
+      <c r="AM5" s="29"/>
+      <c r="AN5" s="30"/>
+      <c r="AO5" s="31"/>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.45">
       <c r="B6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="32"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="31"/>
-      <c r="P6" s="32"/>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="31"/>
-      <c r="S6" s="32"/>
-      <c r="T6" s="33"/>
-      <c r="U6" s="31"/>
-      <c r="V6" s="32"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="31"/>
-      <c r="Y6" s="32"/>
-      <c r="Z6" s="33"/>
-      <c r="AA6" s="31"/>
-      <c r="AB6" s="32"/>
-      <c r="AC6" s="33"/>
-      <c r="AD6" s="31"/>
-      <c r="AE6" s="32"/>
-      <c r="AF6" s="33"/>
-      <c r="AG6" s="31"/>
-      <c r="AH6" s="32"/>
-      <c r="AI6" s="33"/>
-      <c r="AJ6" s="31"/>
-      <c r="AK6" s="32"/>
-      <c r="AL6" s="33"/>
-      <c r="AM6" s="31"/>
-      <c r="AN6" s="32"/>
-      <c r="AO6" s="33"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="31"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="31"/>
+      <c r="X6" s="29"/>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="31"/>
+      <c r="AA6" s="29"/>
+      <c r="AB6" s="30"/>
+      <c r="AC6" s="31"/>
+      <c r="AD6" s="29"/>
+      <c r="AE6" s="30"/>
+      <c r="AF6" s="31"/>
+      <c r="AG6" s="29"/>
+      <c r="AH6" s="30"/>
+      <c r="AI6" s="31"/>
+      <c r="AJ6" s="29"/>
+      <c r="AK6" s="30"/>
+      <c r="AL6" s="31"/>
+      <c r="AM6" s="29"/>
+      <c r="AN6" s="30"/>
+      <c r="AO6" s="31"/>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.45">
       <c r="B7" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="32"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="33"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="32"/>
-      <c r="Q7" s="33"/>
-      <c r="R7" s="31"/>
-      <c r="S7" s="32"/>
-      <c r="T7" s="33"/>
-      <c r="U7" s="31"/>
-      <c r="V7" s="32"/>
-      <c r="W7" s="33"/>
-      <c r="X7" s="31"/>
-      <c r="Y7" s="32"/>
-      <c r="Z7" s="33"/>
-      <c r="AA7" s="31"/>
-      <c r="AB7" s="32"/>
-      <c r="AC7" s="33"/>
-      <c r="AD7" s="31"/>
-      <c r="AE7" s="32"/>
-      <c r="AF7" s="33"/>
-      <c r="AG7" s="31"/>
-      <c r="AH7" s="32"/>
-      <c r="AI7" s="33"/>
-      <c r="AJ7" s="31"/>
-      <c r="AK7" s="32"/>
-      <c r="AL7" s="33"/>
-      <c r="AM7" s="31"/>
-      <c r="AN7" s="32"/>
-      <c r="AO7" s="33"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="30"/>
+      <c r="T7" s="31"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="31"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="31"/>
+      <c r="AA7" s="29"/>
+      <c r="AB7" s="30"/>
+      <c r="AC7" s="31"/>
+      <c r="AD7" s="29"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="31"/>
+      <c r="AG7" s="29"/>
+      <c r="AH7" s="30"/>
+      <c r="AI7" s="31"/>
+      <c r="AJ7" s="29"/>
+      <c r="AK7" s="30"/>
+      <c r="AL7" s="31"/>
+      <c r="AM7" s="29"/>
+      <c r="AN7" s="30"/>
+      <c r="AO7" s="31"/>
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.45">
       <c r="B8" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="31"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="33"/>
-      <c r="O8" s="31"/>
-      <c r="P8" s="32"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="31"/>
-      <c r="S8" s="32"/>
-      <c r="T8" s="33"/>
-      <c r="U8" s="31"/>
-      <c r="V8" s="32"/>
-      <c r="W8" s="33"/>
-      <c r="X8" s="31"/>
-      <c r="Y8" s="32"/>
-      <c r="Z8" s="33"/>
-      <c r="AA8" s="31"/>
-      <c r="AB8" s="32"/>
-      <c r="AC8" s="33"/>
-      <c r="AD8" s="31"/>
-      <c r="AE8" s="32"/>
-      <c r="AF8" s="33"/>
-      <c r="AG8" s="31"/>
-      <c r="AH8" s="32"/>
-      <c r="AI8" s="33"/>
-      <c r="AJ8" s="31"/>
-      <c r="AK8" s="32"/>
-      <c r="AL8" s="33"/>
-      <c r="AM8" s="31"/>
-      <c r="AN8" s="32"/>
-      <c r="AO8" s="33"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="29"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="29"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="31"/>
+      <c r="X8" s="29"/>
+      <c r="Y8" s="30"/>
+      <c r="Z8" s="31"/>
+      <c r="AA8" s="29"/>
+      <c r="AB8" s="30"/>
+      <c r="AC8" s="31"/>
+      <c r="AD8" s="29"/>
+      <c r="AE8" s="30"/>
+      <c r="AF8" s="31"/>
+      <c r="AG8" s="29"/>
+      <c r="AH8" s="30"/>
+      <c r="AI8" s="31"/>
+      <c r="AJ8" s="29"/>
+      <c r="AK8" s="30"/>
+      <c r="AL8" s="31"/>
+      <c r="AM8" s="29"/>
+      <c r="AN8" s="30"/>
+      <c r="AO8" s="31"/>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.45">
       <c r="B9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="32"/>
-      <c r="Q9" s="33"/>
-      <c r="R9" s="31"/>
-      <c r="S9" s="32"/>
-      <c r="T9" s="33"/>
-      <c r="U9" s="31"/>
-      <c r="V9" s="32"/>
-      <c r="W9" s="33"/>
-      <c r="X9" s="31"/>
-      <c r="Y9" s="32"/>
-      <c r="Z9" s="33"/>
-      <c r="AA9" s="31"/>
-      <c r="AB9" s="32"/>
-      <c r="AC9" s="33"/>
-      <c r="AD9" s="31"/>
-      <c r="AE9" s="32"/>
-      <c r="AF9" s="33"/>
-      <c r="AG9" s="31"/>
-      <c r="AH9" s="32"/>
-      <c r="AI9" s="33"/>
-      <c r="AJ9" s="31"/>
-      <c r="AK9" s="32"/>
-      <c r="AL9" s="33"/>
-      <c r="AM9" s="31"/>
-      <c r="AN9" s="32"/>
-      <c r="AO9" s="33"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="29"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="31"/>
+      <c r="X9" s="29"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="31"/>
+      <c r="AA9" s="29"/>
+      <c r="AB9" s="30"/>
+      <c r="AC9" s="31"/>
+      <c r="AD9" s="29"/>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="31"/>
+      <c r="AG9" s="29"/>
+      <c r="AH9" s="30"/>
+      <c r="AI9" s="31"/>
+      <c r="AJ9" s="29"/>
+      <c r="AK9" s="30"/>
+      <c r="AL9" s="31"/>
+      <c r="AM9" s="29"/>
+      <c r="AN9" s="30"/>
+      <c r="AO9" s="31"/>
     </row>
     <row r="10" spans="1:41" ht="76.900000000000006" x14ac:dyDescent="0.45">
       <c r="B10" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="32"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="32"/>
-      <c r="T10" s="33"/>
-      <c r="U10" s="31"/>
-      <c r="V10" s="32"/>
-      <c r="W10" s="33"/>
-      <c r="X10" s="31"/>
-      <c r="Y10" s="32"/>
-      <c r="Z10" s="33"/>
-      <c r="AA10" s="31"/>
-      <c r="AB10" s="32"/>
-      <c r="AC10" s="33"/>
-      <c r="AD10" s="31"/>
-      <c r="AE10" s="32"/>
-      <c r="AF10" s="33"/>
-      <c r="AG10" s="31"/>
-      <c r="AH10" s="32"/>
-      <c r="AI10" s="33"/>
-      <c r="AJ10" s="31"/>
-      <c r="AK10" s="32"/>
-      <c r="AL10" s="33"/>
-      <c r="AM10" s="31"/>
-      <c r="AN10" s="32"/>
-      <c r="AO10" s="33"/>
+        <v>35</v>
+      </c>
+      <c r="C10" s="29"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="30"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="29"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="31"/>
+      <c r="X10" s="29"/>
+      <c r="Y10" s="30"/>
+      <c r="Z10" s="31"/>
+      <c r="AA10" s="29"/>
+      <c r="AB10" s="30"/>
+      <c r="AC10" s="31"/>
+      <c r="AD10" s="29"/>
+      <c r="AE10" s="30"/>
+      <c r="AF10" s="31"/>
+      <c r="AG10" s="29"/>
+      <c r="AH10" s="30"/>
+      <c r="AI10" s="31"/>
+      <c r="AJ10" s="29"/>
+      <c r="AK10" s="30"/>
+      <c r="AL10" s="31"/>
+      <c r="AM10" s="29"/>
+      <c r="AN10" s="30"/>
+      <c r="AO10" s="31"/>
     </row>
     <row r="11" spans="1:41" ht="92.25" x14ac:dyDescent="0.45">
       <c r="B11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="31"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="31"/>
-      <c r="M11" s="32"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="31"/>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="31"/>
-      <c r="S11" s="32"/>
-      <c r="T11" s="33"/>
-      <c r="U11" s="31"/>
-      <c r="V11" s="32"/>
-      <c r="W11" s="33"/>
-      <c r="X11" s="31"/>
-      <c r="Y11" s="32"/>
-      <c r="Z11" s="33"/>
-      <c r="AA11" s="31"/>
-      <c r="AB11" s="32"/>
-      <c r="AC11" s="33"/>
-      <c r="AD11" s="31"/>
-      <c r="AE11" s="32"/>
-      <c r="AF11" s="33"/>
-      <c r="AG11" s="31"/>
-      <c r="AH11" s="32"/>
-      <c r="AI11" s="33"/>
-      <c r="AJ11" s="31"/>
-      <c r="AK11" s="32"/>
-      <c r="AL11" s="33"/>
-      <c r="AM11" s="31"/>
-      <c r="AN11" s="32"/>
-      <c r="AO11" s="33"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="30"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="29"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="29"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="31"/>
+      <c r="X11" s="29"/>
+      <c r="Y11" s="30"/>
+      <c r="Z11" s="31"/>
+      <c r="AA11" s="29"/>
+      <c r="AB11" s="30"/>
+      <c r="AC11" s="31"/>
+      <c r="AD11" s="29"/>
+      <c r="AE11" s="30"/>
+      <c r="AF11" s="31"/>
+      <c r="AG11" s="29"/>
+      <c r="AH11" s="30"/>
+      <c r="AI11" s="31"/>
+      <c r="AJ11" s="29"/>
+      <c r="AK11" s="30"/>
+      <c r="AL11" s="31"/>
+      <c r="AM11" s="29"/>
+      <c r="AN11" s="30"/>
+      <c r="AO11" s="31"/>
     </row>
     <row r="12" spans="1:41" ht="76.900000000000006" x14ac:dyDescent="0.45">
       <c r="B12" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="32"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="31"/>
-      <c r="P12" s="32"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="31"/>
-      <c r="S12" s="32"/>
-      <c r="T12" s="33"/>
-      <c r="U12" s="31"/>
-      <c r="V12" s="32"/>
-      <c r="W12" s="33"/>
-      <c r="X12" s="31"/>
-      <c r="Y12" s="32"/>
-      <c r="Z12" s="33"/>
-      <c r="AA12" s="31"/>
-      <c r="AB12" s="32"/>
-      <c r="AC12" s="33"/>
-      <c r="AD12" s="31"/>
-      <c r="AE12" s="32"/>
-      <c r="AF12" s="33"/>
-      <c r="AG12" s="31"/>
-      <c r="AH12" s="32"/>
-      <c r="AI12" s="33"/>
-      <c r="AJ12" s="31"/>
-      <c r="AK12" s="32"/>
-      <c r="AL12" s="33"/>
-      <c r="AM12" s="31"/>
-      <c r="AN12" s="32"/>
-      <c r="AO12" s="33"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="29"/>
+      <c r="S12" s="30"/>
+      <c r="T12" s="31"/>
+      <c r="U12" s="29"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="31"/>
+      <c r="X12" s="29"/>
+      <c r="Y12" s="30"/>
+      <c r="Z12" s="31"/>
+      <c r="AA12" s="29"/>
+      <c r="AB12" s="30"/>
+      <c r="AC12" s="31"/>
+      <c r="AD12" s="29"/>
+      <c r="AE12" s="30"/>
+      <c r="AF12" s="31"/>
+      <c r="AG12" s="29"/>
+      <c r="AH12" s="30"/>
+      <c r="AI12" s="31"/>
+      <c r="AJ12" s="29"/>
+      <c r="AK12" s="30"/>
+      <c r="AL12" s="31"/>
+      <c r="AM12" s="29"/>
+      <c r="AN12" s="30"/>
+      <c r="AO12" s="31"/>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.45">
       <c r="B13" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="33"/>
-      <c r="O13" s="31"/>
-      <c r="P13" s="32"/>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="31"/>
-      <c r="S13" s="32"/>
-      <c r="T13" s="33"/>
-      <c r="U13" s="31"/>
-      <c r="V13" s="32"/>
-      <c r="W13" s="33"/>
-      <c r="X13" s="31"/>
-      <c r="Y13" s="32"/>
-      <c r="Z13" s="33"/>
-      <c r="AA13" s="31"/>
-      <c r="AB13" s="32"/>
-      <c r="AC13" s="33"/>
-      <c r="AD13" s="31"/>
-      <c r="AE13" s="32"/>
-      <c r="AF13" s="33"/>
-      <c r="AG13" s="31"/>
-      <c r="AH13" s="32"/>
-      <c r="AI13" s="33"/>
-      <c r="AJ13" s="31"/>
-      <c r="AK13" s="32"/>
-      <c r="AL13" s="33"/>
-      <c r="AM13" s="31"/>
-      <c r="AN13" s="32"/>
-      <c r="AO13" s="33"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="30"/>
+      <c r="Q13" s="31"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="30"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="29"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="31"/>
+      <c r="X13" s="29"/>
+      <c r="Y13" s="30"/>
+      <c r="Z13" s="31"/>
+      <c r="AA13" s="29"/>
+      <c r="AB13" s="30"/>
+      <c r="AC13" s="31"/>
+      <c r="AD13" s="29"/>
+      <c r="AE13" s="30"/>
+      <c r="AF13" s="31"/>
+      <c r="AG13" s="29"/>
+      <c r="AH13" s="30"/>
+      <c r="AI13" s="31"/>
+      <c r="AJ13" s="29"/>
+      <c r="AK13" s="30"/>
+      <c r="AL13" s="31"/>
+      <c r="AM13" s="29"/>
+      <c r="AN13" s="30"/>
+      <c r="AO13" s="31"/>
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.45">
       <c r="B14" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="32"/>
-      <c r="N14" s="33"/>
-      <c r="O14" s="31"/>
-      <c r="P14" s="32"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="31"/>
-      <c r="S14" s="32"/>
-      <c r="T14" s="33"/>
-      <c r="U14" s="31"/>
-      <c r="V14" s="32"/>
-      <c r="W14" s="33"/>
-      <c r="X14" s="31"/>
-      <c r="Y14" s="32"/>
-      <c r="Z14" s="33"/>
-      <c r="AA14" s="31"/>
-      <c r="AB14" s="32"/>
-      <c r="AC14" s="33"/>
-      <c r="AD14" s="31"/>
-      <c r="AE14" s="32"/>
-      <c r="AF14" s="33"/>
-      <c r="AG14" s="31"/>
-      <c r="AH14" s="32"/>
-      <c r="AI14" s="33"/>
-      <c r="AJ14" s="31"/>
-      <c r="AK14" s="32"/>
-      <c r="AL14" s="33"/>
-      <c r="AM14" s="31"/>
-      <c r="AN14" s="32"/>
-      <c r="AO14" s="33"/>
+        <v>36</v>
+      </c>
+      <c r="C14" s="29"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="31"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="30"/>
+      <c r="Q14" s="31"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="30"/>
+      <c r="T14" s="31"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="31"/>
+      <c r="X14" s="29"/>
+      <c r="Y14" s="30"/>
+      <c r="Z14" s="31"/>
+      <c r="AA14" s="29"/>
+      <c r="AB14" s="30"/>
+      <c r="AC14" s="31"/>
+      <c r="AD14" s="29"/>
+      <c r="AE14" s="30"/>
+      <c r="AF14" s="31"/>
+      <c r="AG14" s="29"/>
+      <c r="AH14" s="30"/>
+      <c r="AI14" s="31"/>
+      <c r="AJ14" s="29"/>
+      <c r="AK14" s="30"/>
+      <c r="AL14" s="31"/>
+      <c r="AM14" s="29"/>
+      <c r="AN14" s="30"/>
+      <c r="AO14" s="31"/>
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.45">
       <c r="B15" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="32"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="32"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="32"/>
-      <c r="T15" s="33"/>
-      <c r="U15" s="31"/>
-      <c r="V15" s="32"/>
-      <c r="W15" s="33"/>
-      <c r="X15" s="31"/>
-      <c r="Y15" s="32"/>
-      <c r="Z15" s="33"/>
-      <c r="AA15" s="31"/>
-      <c r="AB15" s="32"/>
-      <c r="AC15" s="33"/>
-      <c r="AD15" s="31"/>
-      <c r="AE15" s="32"/>
-      <c r="AF15" s="33"/>
-      <c r="AG15" s="31"/>
-      <c r="AH15" s="32"/>
-      <c r="AI15" s="33"/>
-      <c r="AJ15" s="31"/>
-      <c r="AK15" s="32"/>
-      <c r="AL15" s="33"/>
-      <c r="AM15" s="31"/>
-      <c r="AN15" s="32"/>
-      <c r="AO15" s="33"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="30"/>
+      <c r="Q15" s="31"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="30"/>
+      <c r="T15" s="31"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="30"/>
+      <c r="W15" s="31"/>
+      <c r="X15" s="29"/>
+      <c r="Y15" s="30"/>
+      <c r="Z15" s="31"/>
+      <c r="AA15" s="29"/>
+      <c r="AB15" s="30"/>
+      <c r="AC15" s="31"/>
+      <c r="AD15" s="29"/>
+      <c r="AE15" s="30"/>
+      <c r="AF15" s="31"/>
+      <c r="AG15" s="29"/>
+      <c r="AH15" s="30"/>
+      <c r="AI15" s="31"/>
+      <c r="AJ15" s="29"/>
+      <c r="AK15" s="30"/>
+      <c r="AL15" s="31"/>
+      <c r="AM15" s="29"/>
+      <c r="AN15" s="30"/>
+      <c r="AO15" s="31"/>
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.45">
       <c r="B16" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="31"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
-      <c r="T16" s="33"/>
-      <c r="U16" s="31"/>
-      <c r="V16" s="32"/>
-      <c r="W16" s="33"/>
-      <c r="X16" s="31"/>
-      <c r="Y16" s="32"/>
-      <c r="Z16" s="33"/>
-      <c r="AA16" s="31"/>
-      <c r="AB16" s="32"/>
-      <c r="AC16" s="33"/>
-      <c r="AD16" s="31"/>
-      <c r="AE16" s="32"/>
-      <c r="AF16" s="33"/>
-      <c r="AG16" s="31"/>
-      <c r="AH16" s="32"/>
-      <c r="AI16" s="33"/>
-      <c r="AJ16" s="31"/>
-      <c r="AK16" s="32"/>
-      <c r="AL16" s="33"/>
-      <c r="AM16" s="31"/>
-      <c r="AN16" s="32"/>
-      <c r="AO16" s="33"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="30"/>
+      <c r="Q16" s="31"/>
+      <c r="R16" s="29"/>
+      <c r="S16" s="30"/>
+      <c r="T16" s="31"/>
+      <c r="U16" s="29"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="31"/>
+      <c r="X16" s="29"/>
+      <c r="Y16" s="30"/>
+      <c r="Z16" s="31"/>
+      <c r="AA16" s="29"/>
+      <c r="AB16" s="30"/>
+      <c r="AC16" s="31"/>
+      <c r="AD16" s="29"/>
+      <c r="AE16" s="30"/>
+      <c r="AF16" s="31"/>
+      <c r="AG16" s="29"/>
+      <c r="AH16" s="30"/>
+      <c r="AI16" s="31"/>
+      <c r="AJ16" s="29"/>
+      <c r="AK16" s="30"/>
+      <c r="AL16" s="31"/>
+      <c r="AM16" s="29"/>
+      <c r="AN16" s="30"/>
+      <c r="AO16" s="31"/>
     </row>
     <row r="17" spans="1:41" ht="61.5" x14ac:dyDescent="0.45">
       <c r="B17" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="31"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="32"/>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="31"/>
-      <c r="S17" s="32"/>
-      <c r="T17" s="33"/>
-      <c r="U17" s="31"/>
-      <c r="V17" s="32"/>
-      <c r="W17" s="33"/>
-      <c r="X17" s="31"/>
-      <c r="Y17" s="32"/>
-      <c r="Z17" s="33"/>
-      <c r="AA17" s="31"/>
-      <c r="AB17" s="32"/>
-      <c r="AC17" s="33"/>
-      <c r="AD17" s="31"/>
-      <c r="AE17" s="32"/>
-      <c r="AF17" s="33"/>
-      <c r="AG17" s="31"/>
-      <c r="AH17" s="32"/>
-      <c r="AI17" s="33"/>
-      <c r="AJ17" s="31"/>
-      <c r="AK17" s="32"/>
-      <c r="AL17" s="33"/>
-      <c r="AM17" s="31"/>
-      <c r="AN17" s="32"/>
-      <c r="AO17" s="33"/>
+        <v>37</v>
+      </c>
+      <c r="C17" s="29"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="30"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="30"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="30"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="30"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="29"/>
+      <c r="Y17" s="30"/>
+      <c r="Z17" s="31"/>
+      <c r="AA17" s="29"/>
+      <c r="AB17" s="30"/>
+      <c r="AC17" s="31"/>
+      <c r="AD17" s="29"/>
+      <c r="AE17" s="30"/>
+      <c r="AF17" s="31"/>
+      <c r="AG17" s="29"/>
+      <c r="AH17" s="30"/>
+      <c r="AI17" s="31"/>
+      <c r="AJ17" s="29"/>
+      <c r="AK17" s="30"/>
+      <c r="AL17" s="31"/>
+      <c r="AM17" s="29"/>
+      <c r="AN17" s="30"/>
+      <c r="AO17" s="31"/>
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.45">
       <c r="B18" s="10"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="31"/>
-      <c r="M18" s="32"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="31"/>
-      <c r="P18" s="32"/>
-      <c r="Q18" s="33"/>
-      <c r="R18" s="31"/>
-      <c r="S18" s="32"/>
-      <c r="T18" s="33"/>
-      <c r="U18" s="31"/>
-      <c r="V18" s="32"/>
-      <c r="W18" s="33"/>
-      <c r="X18" s="31"/>
-      <c r="Y18" s="32"/>
-      <c r="Z18" s="33"/>
-      <c r="AA18" s="31"/>
-      <c r="AB18" s="32"/>
-      <c r="AC18" s="33"/>
-      <c r="AD18" s="31"/>
-      <c r="AE18" s="32"/>
-      <c r="AF18" s="33"/>
-      <c r="AG18" s="31"/>
-      <c r="AH18" s="32"/>
-      <c r="AI18" s="33"/>
-      <c r="AJ18" s="31"/>
-      <c r="AK18" s="32"/>
-      <c r="AL18" s="33"/>
-      <c r="AM18" s="31"/>
-      <c r="AN18" s="32"/>
-      <c r="AO18" s="33"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="30"/>
+      <c r="Q18" s="31"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="30"/>
+      <c r="T18" s="31"/>
+      <c r="U18" s="29"/>
+      <c r="V18" s="30"/>
+      <c r="W18" s="31"/>
+      <c r="X18" s="29"/>
+      <c r="Y18" s="30"/>
+      <c r="Z18" s="31"/>
+      <c r="AA18" s="29"/>
+      <c r="AB18" s="30"/>
+      <c r="AC18" s="31"/>
+      <c r="AD18" s="29"/>
+      <c r="AE18" s="30"/>
+      <c r="AF18" s="31"/>
+      <c r="AG18" s="29"/>
+      <c r="AH18" s="30"/>
+      <c r="AI18" s="31"/>
+      <c r="AJ18" s="29"/>
+      <c r="AK18" s="30"/>
+      <c r="AL18" s="31"/>
+      <c r="AM18" s="29"/>
+      <c r="AN18" s="30"/>
+      <c r="AO18" s="31"/>
     </row>
     <row r="19" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1"/>
       <c r="B19" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="38">
+      <c r="C19" s="37">
         <f>AVERAGE(C4:C18)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="39"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="38">
+      <c r="D19" s="38"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="37">
         <f>AVERAGE(F4:F18)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="39"/>
-      <c r="H19" s="40"/>
-      <c r="I19" s="38">
+      <c r="G19" s="38"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="37">
         <f>AVERAGE(I4:I18)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="39"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="38">
+      <c r="J19" s="38"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="37">
         <f>AVERAGE(L4:L18)</f>
         <v>0</v>
       </c>
-      <c r="M19" s="39"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="38">
+      <c r="M19" s="38"/>
+      <c r="N19" s="39"/>
+      <c r="O19" s="37">
         <f>AVERAGE(O4:O18)</f>
         <v>0</v>
       </c>
-      <c r="P19" s="39"/>
-      <c r="Q19" s="40"/>
-      <c r="R19" s="38">
+      <c r="P19" s="38"/>
+      <c r="Q19" s="39"/>
+      <c r="R19" s="37">
         <f>AVERAGE(R4:R18)</f>
         <v>0</v>
       </c>
-      <c r="S19" s="39"/>
-      <c r="T19" s="40"/>
-      <c r="U19" s="38">
+      <c r="S19" s="38"/>
+      <c r="T19" s="39"/>
+      <c r="U19" s="37">
         <f>AVERAGE(U4:U18)</f>
         <v>0</v>
       </c>
-      <c r="V19" s="39"/>
-      <c r="W19" s="40"/>
-      <c r="X19" s="38">
+      <c r="V19" s="38"/>
+      <c r="W19" s="39"/>
+      <c r="X19" s="37">
         <f>AVERAGE(X4:X18)</f>
         <v>0</v>
       </c>
-      <c r="Y19" s="39"/>
-      <c r="Z19" s="40"/>
-      <c r="AA19" s="38">
+      <c r="Y19" s="38"/>
+      <c r="Z19" s="39"/>
+      <c r="AA19" s="37">
         <f>AVERAGE(AA4:AA18)</f>
         <v>0</v>
       </c>
-      <c r="AB19" s="39"/>
-      <c r="AC19" s="40"/>
-      <c r="AD19" s="38">
+      <c r="AB19" s="38"/>
+      <c r="AC19" s="39"/>
+      <c r="AD19" s="37">
         <f>AVERAGE(AD4:AD18)</f>
         <v>0</v>
       </c>
-      <c r="AE19" s="39"/>
-      <c r="AF19" s="40"/>
-      <c r="AG19" s="38">
+      <c r="AE19" s="38"/>
+      <c r="AF19" s="39"/>
+      <c r="AG19" s="37">
         <f>AVERAGE(AG4:AG18)</f>
         <v>0</v>
       </c>
-      <c r="AH19" s="39"/>
-      <c r="AI19" s="40"/>
-      <c r="AJ19" s="38">
+      <c r="AH19" s="38"/>
+      <c r="AI19" s="39"/>
+      <c r="AJ19" s="37">
         <f>AVERAGE(AJ4:AJ18)</f>
         <v>0</v>
       </c>
-      <c r="AK19" s="39"/>
-      <c r="AL19" s="40"/>
-      <c r="AM19" s="38">
+      <c r="AK19" s="38"/>
+      <c r="AL19" s="39"/>
+      <c r="AM19" s="37">
         <f>AVERAGE(AM4:AM18)</f>
         <v>0</v>
       </c>
-      <c r="AN19" s="39"/>
-      <c r="AO19" s="40"/>
+      <c r="AN19" s="38"/>
+      <c r="AO19" s="39"/>
     </row>
     <row r="20" spans="1:41" s="8" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B20" s="7"/>
@@ -4912,24 +4897,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="AM19:AO19"/>
-    <mergeCell ref="X19:Z19"/>
-    <mergeCell ref="AA19:AC19"/>
-    <mergeCell ref="AD19:AF19"/>
-    <mergeCell ref="AG19:AI19"/>
-    <mergeCell ref="AJ19:AL19"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="L19:N19"/>
     <mergeCell ref="O19:Q19"/>
@@ -4939,6 +4906,24 @@
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="F19:H19"/>
     <mergeCell ref="I19:K19"/>
+    <mergeCell ref="AM19:AO19"/>
+    <mergeCell ref="X19:Z19"/>
+    <mergeCell ref="AA19:AC19"/>
+    <mergeCell ref="AD19:AF19"/>
+    <mergeCell ref="AG19:AI19"/>
+    <mergeCell ref="AJ19:AL19"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="I2:K2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/activity/M01A03/M01A03_RadioCurvatura.xlsx
+++ b/activity/M01A03/M01A03_RadioCurvatura.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29304"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D1CFF22-4E1F-4714-89A8-A2D123BD01B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E99961A8-933F-4095-87DE-997BAA2A70F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="12" r:id="rId1"/>
     <sheet name="Detalle" sheetId="10" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Detalle!$B$1:$E$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Detalle!$B$1:$E$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,15 +53,6 @@
   </si>
   <si>
     <t>Requerimiento</t>
-  </si>
-  <si>
-    <t>Capa geográfica puntos eje valle recto</t>
-  </si>
-  <si>
-    <t>Capa geográfica eje recto valle</t>
-  </si>
-  <si>
-    <t>Capa geográfica eje valle suavizado</t>
   </si>
   <si>
     <t>Valores registrados en libro de parámetros</t>
@@ -145,16 +136,34 @@
     <t>Grupo 13</t>
   </si>
   <si>
-    <t>Realizar el suavizado del valle usando arcos circulares y medir su longitud. Formato shapefile con georeferenciación, formato Autodesk AutoCAD y formato como alineamiento Autodesk Civil 3D. En el informe compare las longitudes obtenidas y explique las diferencias.</t>
-  </si>
-  <si>
-    <t>Capas geográficas en /file/shp/</t>
-  </si>
-  <si>
     <t>Informe técnico mostrando las actividades desarrolladas en el orden presentado en esta actividad, junto con los análisis y recomendaciones realizadas, convierta a Adobe Acrobat (.pdf) y guarde en la carpeta /report del repositorio de datos del proyecto.</t>
   </si>
   <si>
     <t>Grupo 14</t>
+  </si>
+  <si>
+    <t>Capa geográfica puntos eje valle recto R.HCMC.NodoValle.shp</t>
+  </si>
+  <si>
+    <t>En el informe compare las longitudes obtenidas y explique las diferencias.</t>
+  </si>
+  <si>
+    <t>Repositorio de proyecto</t>
+  </si>
+  <si>
+    <t>Capas geográficas en /shp
+  RD_EjeValle_v0.shp
+  RD_EjeValleSuavizado_QGIS.shp 
+  RD_EjeValleSuavizado_AutodeskCivil3DClotoide.shp
+  RD_EjeValleSuavizadoBuffer1km.shp
+  RD_EjeValleSuavizadoBuffer1kmUC.shp
+  RD_EjeValleSuavizadoBuffer1kmFalla.shp</t>
+  </si>
+  <si>
+    <t>Dibujos CAD y Civil 3D en /cad
+  RD_EjeValleSuavizado_AutodeskCivil3DClotoide.dxf
+  RD_EjeValleSuavizado_AutodeskCivil3DAligmentAcad.dwg
+  RD_EjeValleSuavizado_AutodeskCivil3DAligment.dwg</t>
   </si>
 </sst>
 </file>
@@ -269,7 +278,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -495,41 +504,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -539,7 +513,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -631,17 +605,6 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2102,51 +2065,51 @@
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
       <c r="F1" s="23" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
     </row>
     <row r="4" spans="2:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="19" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B5" s="11" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C5" s="24">
         <v>5</v>
       </c>
       <c r="D5" s="20">
-        <f>Detalle!C19*C5/5</f>
+        <f>Detalle!C18*C5/5</f>
         <v>0</v>
       </c>
       <c r="E5" s="24"/>
@@ -2157,13 +2120,13 @@
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B6" s="11" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C6" s="24">
         <v>5</v>
       </c>
       <c r="D6" s="20">
-        <f>Detalle!F19*C6/5</f>
+        <f>Detalle!F18*C6/5</f>
         <v>0</v>
       </c>
       <c r="E6" s="24"/>
@@ -2174,13 +2137,13 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B7" s="11" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C7" s="24">
         <v>5</v>
       </c>
       <c r="D7" s="20">
-        <f>Detalle!I19*C7/5</f>
+        <f>Detalle!I18*C7/5</f>
         <v>0</v>
       </c>
       <c r="E7" s="24"/>
@@ -2191,13 +2154,13 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B8" s="11" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C8" s="24">
         <v>5</v>
       </c>
       <c r="D8" s="20">
-        <f>Detalle!L19*C8/5</f>
+        <f>Detalle!L18*C8/5</f>
         <v>0</v>
       </c>
       <c r="E8" s="24"/>
@@ -2208,13 +2171,13 @@
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B9" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C9" s="24">
         <v>5</v>
       </c>
       <c r="D9" s="20">
-        <f>Detalle!O19*C9/5</f>
+        <f>Detalle!O18*C9/5</f>
         <v>0</v>
       </c>
       <c r="E9" s="24"/>
@@ -2225,13 +2188,13 @@
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B10" s="11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C10" s="24">
         <v>5</v>
       </c>
       <c r="D10" s="20">
-        <f>Detalle!R19*C10/5</f>
+        <f>Detalle!R18*C10/5</f>
         <v>0</v>
       </c>
       <c r="E10" s="24"/>
@@ -2242,13 +2205,13 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B11" s="11" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C11" s="24">
         <v>5</v>
       </c>
       <c r="D11" s="20">
-        <f>Detalle!U19*C11/5</f>
+        <f>Detalle!U18*C11/5</f>
         <v>0</v>
       </c>
       <c r="E11" s="24"/>
@@ -2259,13 +2222,13 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B12" s="11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C12" s="24">
         <v>5</v>
       </c>
       <c r="D12" s="20">
-        <f>Detalle!X19*C12/5</f>
+        <f>Detalle!X18*C12/5</f>
         <v>0</v>
       </c>
       <c r="E12" s="24"/>
@@ -2276,13 +2239,13 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B13" s="11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C13" s="24">
         <v>5</v>
       </c>
       <c r="D13" s="20">
-        <f>Detalle!AA19*C13/5</f>
+        <f>Detalle!AA18*C13/5</f>
         <v>0</v>
       </c>
       <c r="E13" s="24"/>
@@ -2293,13 +2256,13 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B14" s="11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C14" s="24">
         <v>5</v>
       </c>
       <c r="D14" s="20">
-        <f>Detalle!AD19*C14/5</f>
+        <f>Detalle!AD18*C14/5</f>
         <v>0</v>
       </c>
       <c r="E14" s="24"/>
@@ -2310,13 +2273,13 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B15" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C15" s="24">
         <v>5</v>
       </c>
       <c r="D15" s="20">
-        <f>Detalle!AG19*C15/5</f>
+        <f>Detalle!AG18*C15/5</f>
         <v>0</v>
       </c>
       <c r="E15" s="24"/>
@@ -2327,13 +2290,13 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B16" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C16" s="24">
         <v>5</v>
       </c>
       <c r="D16" s="20">
-        <f>Detalle!AJ19*C16/5</f>
+        <f>Detalle!AJ18*C16/5</f>
         <v>0</v>
       </c>
       <c r="E16" s="24"/>
@@ -2344,13 +2307,13 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B17" s="11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C17" s="24">
         <v>5</v>
       </c>
       <c r="D17" s="20">
-        <f>Detalle!AM19*C17/5</f>
+        <f>Detalle!AM18*C17/5</f>
         <v>0</v>
       </c>
       <c r="E17" s="24"/>
@@ -2361,13 +2324,13 @@
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B18" s="13" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C18" s="25">
         <v>5</v>
       </c>
       <c r="D18" s="21">
-        <f>Detalle!AP19*C18/5</f>
+        <f>Detalle!AP18*C18/5</f>
         <v>0</v>
       </c>
       <c r="E18" s="25"/>
@@ -2377,21 +2340,21 @@
       </c>
     </row>
     <row r="19" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="36" t="str">
+      <c r="B19" s="33" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M01A03 en GitHub.</v>
       </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="22"/>
@@ -2418,7 +2381,7 @@
   <sheetPr codeName="Hoja1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AR55"/>
+  <dimension ref="A1:AR54"/>
   <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="7" customWidth="1"/>
@@ -2477,101 +2440,101 @@
     </row>
     <row r="2" spans="1:44" s="4" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="37" t="str">
+      <c r="C2" s="34" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="38"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="37" t="str">
+      <c r="D2" s="35"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="34" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="38"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="37" t="str">
+      <c r="G2" s="35"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="34" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="38"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="37" t="str">
+      <c r="J2" s="35"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="34" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="38"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="37" t="str">
+      <c r="M2" s="35"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="34" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="37" t="str">
+      <c r="P2" s="35"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="34" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="S2" s="38"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="37" t="str">
+      <c r="S2" s="35"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="34" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="V2" s="38"/>
-      <c r="W2" s="39"/>
-      <c r="X2" s="37" t="str">
+      <c r="V2" s="35"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="34" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="Y2" s="38"/>
-      <c r="Z2" s="39"/>
-      <c r="AA2" s="37" t="str">
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="36"/>
+      <c r="AA2" s="34" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="39"/>
-      <c r="AD2" s="37" t="str">
+      <c r="AB2" s="35"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="34" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AE2" s="38"/>
-      <c r="AF2" s="39"/>
-      <c r="AG2" s="37" t="str">
+      <c r="AE2" s="35"/>
+      <c r="AF2" s="36"/>
+      <c r="AG2" s="34" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AH2" s="38"/>
-      <c r="AI2" s="39"/>
-      <c r="AJ2" s="37" t="str">
+      <c r="AH2" s="35"/>
+      <c r="AI2" s="36"/>
+      <c r="AJ2" s="34" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AK2" s="38"/>
-      <c r="AL2" s="39"/>
-      <c r="AM2" s="37" t="str">
+      <c r="AK2" s="35"/>
+      <c r="AL2" s="36"/>
+      <c r="AM2" s="34" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AN2" s="38"/>
-      <c r="AO2" s="39"/>
-      <c r="AP2" s="37" t="str">
+      <c r="AN2" s="35"/>
+      <c r="AO2" s="36"/>
+      <c r="AP2" s="34" t="str">
         <f>Calificacion!$B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AQ2" s="38"/>
-      <c r="AR2" s="39"/>
+      <c r="AQ2" s="35"/>
+      <c r="AR2" s="36"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B3" s="43"/>
+      <c r="B3" s="40"/>
       <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E3" s="16" t="s">
         <v>0</v>
@@ -2580,7 +2543,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H3" s="16" t="s">
         <v>0</v>
@@ -2589,7 +2552,7 @@
         <v>1</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K3" s="16" t="s">
         <v>0</v>
@@ -2598,7 +2561,7 @@
         <v>1</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N3" s="16" t="s">
         <v>0</v>
@@ -2607,7 +2570,7 @@
         <v>1</v>
       </c>
       <c r="P3" s="15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q3" s="16" t="s">
         <v>0</v>
@@ -2616,7 +2579,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" s="16" t="s">
         <v>0</v>
@@ -2625,7 +2588,7 @@
         <v>1</v>
       </c>
       <c r="V3" s="15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W3" s="16" t="s">
         <v>0</v>
@@ -2634,7 +2597,7 @@
         <v>1</v>
       </c>
       <c r="Y3" s="15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z3" s="16" t="s">
         <v>0</v>
@@ -2643,7 +2606,7 @@
         <v>1</v>
       </c>
       <c r="AB3" s="15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC3" s="16" t="s">
         <v>0</v>
@@ -2652,7 +2615,7 @@
         <v>1</v>
       </c>
       <c r="AE3" s="15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF3" s="16" t="s">
         <v>0</v>
@@ -2661,7 +2624,7 @@
         <v>1</v>
       </c>
       <c r="AH3" s="15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AI3" s="16" t="s">
         <v>0</v>
@@ -2670,7 +2633,7 @@
         <v>1</v>
       </c>
       <c r="AK3" s="15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AL3" s="16" t="s">
         <v>0</v>
@@ -2679,7 +2642,7 @@
         <v>1</v>
       </c>
       <c r="AN3" s="15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AO3" s="16" t="s">
         <v>0</v>
@@ -2688,7 +2651,7 @@
         <v>1</v>
       </c>
       <c r="AQ3" s="15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AR3" s="16" t="s">
         <v>0</v>
@@ -2696,7 +2659,7 @@
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B4" s="9" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="C4" s="26">
         <v>0</v>
@@ -2769,9 +2732,9 @@
       <c r="AQ4" s="27"/>
       <c r="AR4" s="28"/>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:44" ht="107.65" x14ac:dyDescent="0.45">
       <c r="B5" s="9" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="27"/>
@@ -2816,9 +2779,9 @@
       <c r="AQ5" s="27"/>
       <c r="AR5" s="28"/>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
       <c r="B6" s="9" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="27"/>
@@ -2865,7 +2828,7 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B7" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C7" s="26"/>
       <c r="D7" s="27"/>
@@ -2912,7 +2875,7 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B8" s="9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="27"/>
@@ -2959,7 +2922,7 @@
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B9" s="9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C9" s="26"/>
       <c r="D9" s="27"/>
@@ -3004,7 +2967,7 @@
       <c r="AQ9" s="27"/>
       <c r="AR9" s="28"/>
     </row>
-    <row r="10" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B10" s="9" t="s">
         <v>35</v>
       </c>
@@ -3053,7 +3016,7 @@
     </row>
     <row r="11" spans="1:44" ht="92.25" x14ac:dyDescent="0.45">
       <c r="B11" s="9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C11" s="26"/>
       <c r="D11" s="27"/>
@@ -3100,7 +3063,7 @@
     </row>
     <row r="12" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
       <c r="B12" s="9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="27"/>
@@ -3147,7 +3110,7 @@
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B13" s="9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C13" s="26"/>
       <c r="D13" s="27"/>
@@ -3194,7 +3157,7 @@
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B14" s="9" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C14" s="26"/>
       <c r="D14" s="27"/>
@@ -3241,7 +3204,7 @@
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B15" s="9" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C15" s="26"/>
       <c r="D15" s="27"/>
@@ -3286,9 +3249,9 @@
       <c r="AQ15" s="27"/>
       <c r="AR15" s="28"/>
     </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
       <c r="B16" s="9" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C16" s="26"/>
       <c r="D16" s="27"/>
@@ -3333,9 +3296,9 @@
       <c r="AQ16" s="27"/>
       <c r="AR16" s="28"/>
     </row>
-    <row r="17" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
-      <c r="B17" s="9" t="s">
-        <v>37</v>
+    <row r="17" spans="1:44" x14ac:dyDescent="0.45">
+      <c r="B17" s="29" t="s">
+        <v>36</v>
       </c>
       <c r="C17" s="26"/>
       <c r="D17" s="27"/>
@@ -3380,140 +3343,140 @@
       <c r="AQ17" s="27"/>
       <c r="AR17" s="28"/>
     </row>
-    <row r="18" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B18" s="29"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="31"/>
-      <c r="N18" s="32"/>
-      <c r="O18" s="30"/>
-      <c r="P18" s="31"/>
-      <c r="Q18" s="32"/>
-      <c r="R18" s="30"/>
-      <c r="S18" s="31"/>
-      <c r="T18" s="32"/>
-      <c r="U18" s="30"/>
-      <c r="V18" s="31"/>
-      <c r="W18" s="32"/>
-      <c r="X18" s="30"/>
-      <c r="Y18" s="31"/>
-      <c r="Z18" s="32"/>
-      <c r="AA18" s="30"/>
-      <c r="AB18" s="31"/>
-      <c r="AC18" s="32"/>
-      <c r="AD18" s="30"/>
-      <c r="AE18" s="31"/>
-      <c r="AF18" s="32"/>
-      <c r="AG18" s="30"/>
-      <c r="AH18" s="31"/>
-      <c r="AI18" s="32"/>
-      <c r="AJ18" s="30"/>
-      <c r="AK18" s="31"/>
-      <c r="AL18" s="32"/>
-      <c r="AM18" s="30"/>
-      <c r="AN18" s="31"/>
-      <c r="AO18" s="32"/>
-      <c r="AP18" s="30"/>
-      <c r="AQ18" s="31"/>
-      <c r="AR18" s="32"/>
-    </row>
-    <row r="19" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="1"/>
-      <c r="B19" s="33" t="s">
+    <row r="18" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="1"/>
+      <c r="B18" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="40">
-        <f>AVERAGE(C4:C18)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="40"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="40">
-        <f>AVERAGE(F4:F18)</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="40"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="40">
-        <f>AVERAGE(I4:I18)</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="40"/>
-      <c r="K19" s="41"/>
-      <c r="L19" s="40">
-        <f>AVERAGE(L4:L18)</f>
-        <v>0</v>
-      </c>
-      <c r="M19" s="40"/>
-      <c r="N19" s="41"/>
-      <c r="O19" s="40">
-        <f>AVERAGE(O4:O18)</f>
-        <v>0</v>
-      </c>
-      <c r="P19" s="40"/>
-      <c r="Q19" s="41"/>
-      <c r="R19" s="40">
-        <f>AVERAGE(R4:R18)</f>
-        <v>0</v>
-      </c>
-      <c r="S19" s="40"/>
-      <c r="T19" s="41"/>
-      <c r="U19" s="40">
-        <f>AVERAGE(U4:U18)</f>
-        <v>0</v>
-      </c>
-      <c r="V19" s="40"/>
-      <c r="W19" s="41"/>
-      <c r="X19" s="40">
-        <f>AVERAGE(X4:X18)</f>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="40"/>
-      <c r="Z19" s="41"/>
-      <c r="AA19" s="40">
-        <f>AVERAGE(AA4:AA18)</f>
-        <v>0</v>
-      </c>
-      <c r="AB19" s="40"/>
-      <c r="AC19" s="41"/>
-      <c r="AD19" s="40">
-        <f>AVERAGE(AD4:AD18)</f>
-        <v>0</v>
-      </c>
-      <c r="AE19" s="40"/>
-      <c r="AF19" s="41"/>
-      <c r="AG19" s="40">
-        <f>AVERAGE(AG4:AG18)</f>
-        <v>0</v>
-      </c>
-      <c r="AH19" s="40"/>
-      <c r="AI19" s="41"/>
-      <c r="AJ19" s="40">
-        <f>AVERAGE(AJ4:AJ18)</f>
-        <v>0</v>
-      </c>
-      <c r="AK19" s="40"/>
-      <c r="AL19" s="41"/>
-      <c r="AM19" s="40">
-        <f>AVERAGE(AM4:AM18)</f>
-        <v>0</v>
-      </c>
-      <c r="AN19" s="40"/>
-      <c r="AO19" s="41"/>
-      <c r="AP19" s="40">
-        <f>AVERAGE(AP4:AP18)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ19" s="40"/>
-      <c r="AR19" s="41"/>
+      <c r="C18" s="37">
+        <f>AVERAGE(C4:C17)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="37"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="37">
+        <f>AVERAGE(F4:F17)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="37"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="37">
+        <f>AVERAGE(I4:I17)</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="37"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="37">
+        <f>AVERAGE(L4:L17)</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="37"/>
+      <c r="N18" s="38"/>
+      <c r="O18" s="37">
+        <f>AVERAGE(O4:O17)</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="37"/>
+      <c r="Q18" s="38"/>
+      <c r="R18" s="37">
+        <f>AVERAGE(R4:R17)</f>
+        <v>0</v>
+      </c>
+      <c r="S18" s="37"/>
+      <c r="T18" s="38"/>
+      <c r="U18" s="37">
+        <f>AVERAGE(U4:U17)</f>
+        <v>0</v>
+      </c>
+      <c r="V18" s="37"/>
+      <c r="W18" s="38"/>
+      <c r="X18" s="37">
+        <f>AVERAGE(X4:X17)</f>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="37"/>
+      <c r="Z18" s="38"/>
+      <c r="AA18" s="37">
+        <f>AVERAGE(AA4:AA17)</f>
+        <v>0</v>
+      </c>
+      <c r="AB18" s="37"/>
+      <c r="AC18" s="38"/>
+      <c r="AD18" s="37">
+        <f>AVERAGE(AD4:AD17)</f>
+        <v>0</v>
+      </c>
+      <c r="AE18" s="37"/>
+      <c r="AF18" s="38"/>
+      <c r="AG18" s="37">
+        <f>AVERAGE(AG4:AG17)</f>
+        <v>0</v>
+      </c>
+      <c r="AH18" s="37"/>
+      <c r="AI18" s="38"/>
+      <c r="AJ18" s="37">
+        <f>AVERAGE(AJ4:AJ17)</f>
+        <v>0</v>
+      </c>
+      <c r="AK18" s="37"/>
+      <c r="AL18" s="38"/>
+      <c r="AM18" s="37">
+        <f>AVERAGE(AM4:AM17)</f>
+        <v>0</v>
+      </c>
+      <c r="AN18" s="37"/>
+      <c r="AO18" s="38"/>
+      <c r="AP18" s="37">
+        <f>AVERAGE(AP4:AP17)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="37"/>
+      <c r="AR18" s="38"/>
+    </row>
+    <row r="19" spans="1:44" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B19" s="6"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="5"/>
+      <c r="Y19" s="5"/>
+      <c r="Z19" s="5"/>
+      <c r="AA19" s="5"/>
+      <c r="AB19" s="5"/>
+      <c r="AC19" s="5"/>
+      <c r="AD19" s="5"/>
+      <c r="AE19" s="5"/>
+      <c r="AF19" s="5"/>
+      <c r="AG19" s="5"/>
+      <c r="AH19" s="5"/>
+      <c r="AI19" s="5"/>
+      <c r="AJ19" s="5"/>
+      <c r="AK19" s="5"/>
+      <c r="AL19" s="5"/>
+      <c r="AM19" s="5"/>
+      <c r="AN19" s="5"/>
+      <c r="AO19" s="5"/>
+      <c r="AP19" s="5"/>
+      <c r="AQ19" s="5"/>
+      <c r="AR19" s="5"/>
     </row>
     <row r="20" spans="1:44" s="7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B20" s="6"/>
@@ -5090,74 +5053,8 @@
       <c r="AQ54" s="5"/>
       <c r="AR54" s="5"/>
     </row>
-    <row r="55" spans="2:44" s="7" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B55" s="6"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
-      <c r="I55" s="5"/>
-      <c r="J55" s="5"/>
-      <c r="K55" s="5"/>
-      <c r="L55" s="5"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="5"/>
-      <c r="O55" s="5"/>
-      <c r="P55" s="5"/>
-      <c r="Q55" s="5"/>
-      <c r="R55" s="5"/>
-      <c r="S55" s="5"/>
-      <c r="T55" s="5"/>
-      <c r="U55" s="5"/>
-      <c r="V55" s="5"/>
-      <c r="W55" s="5"/>
-      <c r="X55" s="5"/>
-      <c r="Y55" s="5"/>
-      <c r="Z55" s="5"/>
-      <c r="AA55" s="5"/>
-      <c r="AB55" s="5"/>
-      <c r="AC55" s="5"/>
-      <c r="AD55" s="5"/>
-      <c r="AE55" s="5"/>
-      <c r="AF55" s="5"/>
-      <c r="AG55" s="5"/>
-      <c r="AH55" s="5"/>
-      <c r="AI55" s="5"/>
-      <c r="AJ55" s="5"/>
-      <c r="AK55" s="5"/>
-      <c r="AL55" s="5"/>
-      <c r="AM55" s="5"/>
-      <c r="AN55" s="5"/>
-      <c r="AO55" s="5"/>
-      <c r="AP55" s="5"/>
-      <c r="AQ55" s="5"/>
-      <c r="AR55" s="5"/>
-    </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AP19:AR19"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="R19:T19"/>
-    <mergeCell ref="U19:W19"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="AM19:AO19"/>
-    <mergeCell ref="X19:Z19"/>
-    <mergeCell ref="AA19:AC19"/>
-    <mergeCell ref="AD19:AF19"/>
-    <mergeCell ref="AG19:AI19"/>
-    <mergeCell ref="AJ19:AL19"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="X2:Z2"/>
     <mergeCell ref="O2:Q2"/>
@@ -5166,6 +5063,27 @@
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="I2:K2"/>
+    <mergeCell ref="AJ18:AL18"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="AP18:AR18"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="R18:T18"/>
+    <mergeCell ref="U18:W18"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="AM18:AO18"/>
+    <mergeCell ref="X18:Z18"/>
+    <mergeCell ref="AA18:AC18"/>
+    <mergeCell ref="AD18:AF18"/>
+    <mergeCell ref="AG18:AI18"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/activity/M01A03/M01A03_RadioCurvatura.xlsx
+++ b/activity/M01A03/M01A03_RadioCurvatura.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E99961A8-933F-4095-87DE-997BAA2A70F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEC9A03-29DD-4084-8E08-71FB68136D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Detalle" sheetId="10" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Detalle!$B$1:$E$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Detalle!$B$1:$E$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="38">
   <si>
     <t>Observaciones</t>
   </si>
@@ -142,28 +142,26 @@
     <t>Grupo 14</t>
   </si>
   <si>
-    <t>Capa geográfica puntos eje valle recto R.HCMC.NodoValle.shp</t>
-  </si>
-  <si>
     <t>En el informe compare las longitudes obtenidas y explique las diferencias.</t>
   </si>
   <si>
     <t>Repositorio de proyecto</t>
   </si>
   <si>
+    <t>Dibujos CAD y Civil 3D en /cad
+  RD_EjeValleSuavizado_AutodeskCivil3DClotoide.dxf
+  RD_EjeValleSuavizado_AutodeskCivil3DAligmentAcad.dwg
+  RD_EjeValleSuavizado_AutodeskCivil3DAligment.dwg</t>
+  </si>
+  <si>
     <t>Capas geográficas en /shp
+  R.HCMC.NodoValle.shp  
   RD_EjeValle_v0.shp
   RD_EjeValleSuavizado_QGIS.shp 
   RD_EjeValleSuavizado_AutodeskCivil3DClotoide.shp
   RD_EjeValleSuavizadoBuffer1km.shp
   RD_EjeValleSuavizadoBuffer1kmUC.shp
   RD_EjeValleSuavizadoBuffer1kmFalla.shp</t>
-  </si>
-  <si>
-    <t>Dibujos CAD y Civil 3D en /cad
-  RD_EjeValleSuavizado_AutodeskCivil3DClotoide.dxf
-  RD_EjeValleSuavizado_AutodeskCivil3DAligmentAcad.dwg
-  RD_EjeValleSuavizado_AutodeskCivil3DAligment.dwg</t>
   </si>
 </sst>
 </file>
@@ -2109,7 +2107,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="20">
-        <f>Detalle!C18*C5/5</f>
+        <f>Detalle!C17*C5/5</f>
         <v>0</v>
       </c>
       <c r="E5" s="24"/>
@@ -2126,7 +2124,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="20">
-        <f>Detalle!F18*C6/5</f>
+        <f>Detalle!F17*C6/5</f>
         <v>0</v>
       </c>
       <c r="E6" s="24"/>
@@ -2143,7 +2141,7 @@
         <v>5</v>
       </c>
       <c r="D7" s="20">
-        <f>Detalle!I18*C7/5</f>
+        <f>Detalle!I17*C7/5</f>
         <v>0</v>
       </c>
       <c r="E7" s="24"/>
@@ -2160,7 +2158,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="20">
-        <f>Detalle!L18*C8/5</f>
+        <f>Detalle!L17*C8/5</f>
         <v>0</v>
       </c>
       <c r="E8" s="24"/>
@@ -2177,7 +2175,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="20">
-        <f>Detalle!O18*C9/5</f>
+        <f>Detalle!O17*C9/5</f>
         <v>0</v>
       </c>
       <c r="E9" s="24"/>
@@ -2194,7 +2192,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="20">
-        <f>Detalle!R18*C10/5</f>
+        <f>Detalle!R17*C10/5</f>
         <v>0</v>
       </c>
       <c r="E10" s="24"/>
@@ -2211,7 +2209,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="20">
-        <f>Detalle!U18*C11/5</f>
+        <f>Detalle!U17*C11/5</f>
         <v>0</v>
       </c>
       <c r="E11" s="24"/>
@@ -2228,7 +2226,7 @@
         <v>5</v>
       </c>
       <c r="D12" s="20">
-        <f>Detalle!X18*C12/5</f>
+        <f>Detalle!X17*C12/5</f>
         <v>0</v>
       </c>
       <c r="E12" s="24"/>
@@ -2245,7 +2243,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="20">
-        <f>Detalle!AA18*C13/5</f>
+        <f>Detalle!AA17*C13/5</f>
         <v>0</v>
       </c>
       <c r="E13" s="24"/>
@@ -2262,7 +2260,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="20">
-        <f>Detalle!AD18*C14/5</f>
+        <f>Detalle!AD17*C14/5</f>
         <v>0</v>
       </c>
       <c r="E14" s="24"/>
@@ -2279,7 +2277,7 @@
         <v>5</v>
       </c>
       <c r="D15" s="20">
-        <f>Detalle!AG18*C15/5</f>
+        <f>Detalle!AG17*C15/5</f>
         <v>0</v>
       </c>
       <c r="E15" s="24"/>
@@ -2296,7 +2294,7 @@
         <v>5</v>
       </c>
       <c r="D16" s="20">
-        <f>Detalle!AJ18*C16/5</f>
+        <f>Detalle!AJ17*C16/5</f>
         <v>0</v>
       </c>
       <c r="E16" s="24"/>
@@ -2313,7 +2311,7 @@
         <v>5</v>
       </c>
       <c r="D17" s="20">
-        <f>Detalle!AM18*C17/5</f>
+        <f>Detalle!AM17*C17/5</f>
         <v>0</v>
       </c>
       <c r="E17" s="24"/>
@@ -2330,7 +2328,7 @@
         <v>5</v>
       </c>
       <c r="D18" s="21">
-        <f>Detalle!AP18*C18/5</f>
+        <f>Detalle!AP17*C18/5</f>
         <v>0</v>
       </c>
       <c r="E18" s="25"/>
@@ -2381,7 +2379,7 @@
   <sheetPr codeName="Hoja1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AR54"/>
+  <dimension ref="A1:AR53"/>
   <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="7" customWidth="1"/>
@@ -2657,9 +2655,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:44" ht="123" x14ac:dyDescent="0.45">
       <c r="B4" s="9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C4" s="26">
         <v>0</v>
@@ -2732,9 +2730,9 @@
       <c r="AQ4" s="27"/>
       <c r="AR4" s="28"/>
     </row>
-    <row r="5" spans="1:44" ht="107.65" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
       <c r="B5" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="27"/>
@@ -2779,9 +2777,9 @@
       <c r="AQ5" s="27"/>
       <c r="AR5" s="28"/>
     </row>
-    <row r="6" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B6" s="9" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="27"/>
@@ -2828,7 +2826,7 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B7" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="26"/>
       <c r="D7" s="27"/>
@@ -2875,7 +2873,7 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B8" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="27"/>
@@ -2920,9 +2918,9 @@
       <c r="AQ8" s="27"/>
       <c r="AR8" s="28"/>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B9" s="9" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C9" s="26"/>
       <c r="D9" s="27"/>
@@ -2967,9 +2965,9 @@
       <c r="AQ9" s="27"/>
       <c r="AR9" s="28"/>
     </row>
-    <row r="10" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:44" ht="92.25" x14ac:dyDescent="0.45">
       <c r="B10" s="9" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="27"/>
@@ -3014,9 +3012,9 @@
       <c r="AQ10" s="27"/>
       <c r="AR10" s="28"/>
     </row>
-    <row r="11" spans="1:44" ht="92.25" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
       <c r="B11" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="26"/>
       <c r="D11" s="27"/>
@@ -3061,9 +3059,9 @@
       <c r="AQ11" s="27"/>
       <c r="AR11" s="28"/>
     </row>
-    <row r="12" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B12" s="9" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="27"/>
@@ -3110,7 +3108,7 @@
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B13" s="9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="26"/>
       <c r="D13" s="27"/>
@@ -3157,7 +3155,7 @@
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B14" s="9" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C14" s="26"/>
       <c r="D14" s="27"/>
@@ -3202,9 +3200,9 @@
       <c r="AQ14" s="27"/>
       <c r="AR14" s="28"/>
     </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
       <c r="B15" s="9" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C15" s="26"/>
       <c r="D15" s="27"/>
@@ -3249,9 +3247,9 @@
       <c r="AQ15" s="27"/>
       <c r="AR15" s="28"/>
     </row>
-    <row r="16" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
-      <c r="B16" s="9" t="s">
-        <v>32</v>
+    <row r="16" spans="1:44" x14ac:dyDescent="0.45">
+      <c r="B16" s="29" t="s">
+        <v>35</v>
       </c>
       <c r="C16" s="26"/>
       <c r="D16" s="27"/>
@@ -3296,142 +3294,140 @@
       <c r="AQ16" s="27"/>
       <c r="AR16" s="28"/>
     </row>
-    <row r="17" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B17" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="27"/>
-      <c r="N17" s="28"/>
-      <c r="O17" s="26"/>
-      <c r="P17" s="27"/>
-      <c r="Q17" s="28"/>
-      <c r="R17" s="26"/>
-      <c r="S17" s="27"/>
-      <c r="T17" s="28"/>
-      <c r="U17" s="26"/>
-      <c r="V17" s="27"/>
-      <c r="W17" s="28"/>
-      <c r="X17" s="26"/>
-      <c r="Y17" s="27"/>
-      <c r="Z17" s="28"/>
-      <c r="AA17" s="26"/>
-      <c r="AB17" s="27"/>
-      <c r="AC17" s="28"/>
-      <c r="AD17" s="26"/>
-      <c r="AE17" s="27"/>
-      <c r="AF17" s="28"/>
-      <c r="AG17" s="26"/>
-      <c r="AH17" s="27"/>
-      <c r="AI17" s="28"/>
-      <c r="AJ17" s="26"/>
-      <c r="AK17" s="27"/>
-      <c r="AL17" s="28"/>
-      <c r="AM17" s="26"/>
-      <c r="AN17" s="27"/>
-      <c r="AO17" s="28"/>
-      <c r="AP17" s="26"/>
-      <c r="AQ17" s="27"/>
-      <c r="AR17" s="28"/>
-    </row>
-    <row r="18" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="1"/>
-      <c r="B18" s="30" t="s">
+    <row r="17" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="1"/>
+      <c r="B17" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="37">
-        <f>AVERAGE(C4:C17)</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="37"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="37">
-        <f>AVERAGE(F4:F17)</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="37"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="37">
-        <f>AVERAGE(I4:I17)</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="37"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="37">
-        <f>AVERAGE(L4:L17)</f>
-        <v>0</v>
-      </c>
-      <c r="M18" s="37"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="37">
-        <f>AVERAGE(O4:O17)</f>
-        <v>0</v>
-      </c>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="38"/>
-      <c r="R18" s="37">
-        <f>AVERAGE(R4:R17)</f>
-        <v>0</v>
-      </c>
-      <c r="S18" s="37"/>
-      <c r="T18" s="38"/>
-      <c r="U18" s="37">
-        <f>AVERAGE(U4:U17)</f>
-        <v>0</v>
-      </c>
-      <c r="V18" s="37"/>
-      <c r="W18" s="38"/>
-      <c r="X18" s="37">
-        <f>AVERAGE(X4:X17)</f>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="37"/>
-      <c r="Z18" s="38"/>
-      <c r="AA18" s="37">
-        <f>AVERAGE(AA4:AA17)</f>
-        <v>0</v>
-      </c>
-      <c r="AB18" s="37"/>
-      <c r="AC18" s="38"/>
-      <c r="AD18" s="37">
-        <f>AVERAGE(AD4:AD17)</f>
-        <v>0</v>
-      </c>
-      <c r="AE18" s="37"/>
-      <c r="AF18" s="38"/>
-      <c r="AG18" s="37">
-        <f>AVERAGE(AG4:AG17)</f>
-        <v>0</v>
-      </c>
-      <c r="AH18" s="37"/>
-      <c r="AI18" s="38"/>
-      <c r="AJ18" s="37">
-        <f>AVERAGE(AJ4:AJ17)</f>
-        <v>0</v>
-      </c>
-      <c r="AK18" s="37"/>
-      <c r="AL18" s="38"/>
-      <c r="AM18" s="37">
-        <f>AVERAGE(AM4:AM17)</f>
-        <v>0</v>
-      </c>
-      <c r="AN18" s="37"/>
-      <c r="AO18" s="38"/>
-      <c r="AP18" s="37">
-        <f>AVERAGE(AP4:AP17)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ18" s="37"/>
-      <c r="AR18" s="38"/>
+      <c r="C17" s="37">
+        <f>AVERAGE(C4:C16)</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="37"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="37">
+        <f>AVERAGE(F4:F16)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="37"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="37">
+        <f>AVERAGE(I4:I16)</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="37"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="37">
+        <f>AVERAGE(L4:L16)</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="37"/>
+      <c r="N17" s="38"/>
+      <c r="O17" s="37">
+        <f>AVERAGE(O4:O16)</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="37"/>
+      <c r="Q17" s="38"/>
+      <c r="R17" s="37">
+        <f>AVERAGE(R4:R16)</f>
+        <v>0</v>
+      </c>
+      <c r="S17" s="37"/>
+      <c r="T17" s="38"/>
+      <c r="U17" s="37">
+        <f>AVERAGE(U4:U16)</f>
+        <v>0</v>
+      </c>
+      <c r="V17" s="37"/>
+      <c r="W17" s="38"/>
+      <c r="X17" s="37">
+        <f>AVERAGE(X4:X16)</f>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="37"/>
+      <c r="Z17" s="38"/>
+      <c r="AA17" s="37">
+        <f>AVERAGE(AA4:AA16)</f>
+        <v>0</v>
+      </c>
+      <c r="AB17" s="37"/>
+      <c r="AC17" s="38"/>
+      <c r="AD17" s="37">
+        <f>AVERAGE(AD4:AD16)</f>
+        <v>0</v>
+      </c>
+      <c r="AE17" s="37"/>
+      <c r="AF17" s="38"/>
+      <c r="AG17" s="37">
+        <f>AVERAGE(AG4:AG16)</f>
+        <v>0</v>
+      </c>
+      <c r="AH17" s="37"/>
+      <c r="AI17" s="38"/>
+      <c r="AJ17" s="37">
+        <f>AVERAGE(AJ4:AJ16)</f>
+        <v>0</v>
+      </c>
+      <c r="AK17" s="37"/>
+      <c r="AL17" s="38"/>
+      <c r="AM17" s="37">
+        <f>AVERAGE(AM4:AM16)</f>
+        <v>0</v>
+      </c>
+      <c r="AN17" s="37"/>
+      <c r="AO17" s="38"/>
+      <c r="AP17" s="37">
+        <f>AVERAGE(AP4:AP16)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="37"/>
+      <c r="AR17" s="38"/>
+    </row>
+    <row r="18" spans="1:44" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B18" s="6"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
+      <c r="Z18" s="5"/>
+      <c r="AA18" s="5"/>
+      <c r="AB18" s="5"/>
+      <c r="AC18" s="5"/>
+      <c r="AD18" s="5"/>
+      <c r="AE18" s="5"/>
+      <c r="AF18" s="5"/>
+      <c r="AG18" s="5"/>
+      <c r="AH18" s="5"/>
+      <c r="AI18" s="5"/>
+      <c r="AJ18" s="5"/>
+      <c r="AK18" s="5"/>
+      <c r="AL18" s="5"/>
+      <c r="AM18" s="5"/>
+      <c r="AN18" s="5"/>
+      <c r="AO18" s="5"/>
+      <c r="AP18" s="5"/>
+      <c r="AQ18" s="5"/>
+      <c r="AR18" s="5"/>
     </row>
     <row r="19" spans="1:44" s="7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B19" s="6"/>
@@ -5008,53 +5004,29 @@
       <c r="AQ53" s="5"/>
       <c r="AR53" s="5"/>
     </row>
-    <row r="54" spans="2:44" s="7" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B54" s="6"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
-      <c r="I54" s="5"/>
-      <c r="J54" s="5"/>
-      <c r="K54" s="5"/>
-      <c r="L54" s="5"/>
-      <c r="M54" s="5"/>
-      <c r="N54" s="5"/>
-      <c r="O54" s="5"/>
-      <c r="P54" s="5"/>
-      <c r="Q54" s="5"/>
-      <c r="R54" s="5"/>
-      <c r="S54" s="5"/>
-      <c r="T54" s="5"/>
-      <c r="U54" s="5"/>
-      <c r="V54" s="5"/>
-      <c r="W54" s="5"/>
-      <c r="X54" s="5"/>
-      <c r="Y54" s="5"/>
-      <c r="Z54" s="5"/>
-      <c r="AA54" s="5"/>
-      <c r="AB54" s="5"/>
-      <c r="AC54" s="5"/>
-      <c r="AD54" s="5"/>
-      <c r="AE54" s="5"/>
-      <c r="AF54" s="5"/>
-      <c r="AG54" s="5"/>
-      <c r="AH54" s="5"/>
-      <c r="AI54" s="5"/>
-      <c r="AJ54" s="5"/>
-      <c r="AK54" s="5"/>
-      <c r="AL54" s="5"/>
-      <c r="AM54" s="5"/>
-      <c r="AN54" s="5"/>
-      <c r="AO54" s="5"/>
-      <c r="AP54" s="5"/>
-      <c r="AQ54" s="5"/>
-      <c r="AR54" s="5"/>
-    </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="AP17:AR17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="R17:T17"/>
+    <mergeCell ref="U17:W17"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="AM17:AO17"/>
+    <mergeCell ref="X17:Z17"/>
+    <mergeCell ref="AA17:AC17"/>
+    <mergeCell ref="AD17:AF17"/>
+    <mergeCell ref="AG17:AI17"/>
+    <mergeCell ref="AJ17:AL17"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="X2:Z2"/>
     <mergeCell ref="O2:Q2"/>
@@ -5063,27 +5035,6 @@
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="I2:K2"/>
-    <mergeCell ref="AJ18:AL18"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AP18:AR18"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="R18:T18"/>
-    <mergeCell ref="U18:W18"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="AM18:AO18"/>
-    <mergeCell ref="X18:Z18"/>
-    <mergeCell ref="AA18:AC18"/>
-    <mergeCell ref="AD18:AF18"/>
-    <mergeCell ref="AG18:AI18"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
